--- a/feladvanyok.xlsx
+++ b/feladvanyok.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a3b2d023d0b90a2/Dokumentumok/Rokonszavak/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a3b2d023d0b90a2/Dokumentumok/GitHub/rokonszavak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_4BC928A0A355CC1831E4553E7CBF07CDD619E1D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88C53B5C-FD94-4B47-B9C2-AD49D1DE2B38}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_4BC928A0A355CC1831E4553E7CBF07CDD619E1D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{628C337C-280F-4B15-A767-E1BC83D40D2F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útmutató" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Segéd" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="Játék" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="468">
   <si>
     <t>Rokonszavak – feladványbank és gyakorlólap</t>
   </si>
@@ -1431,6 +1431,18 @@
   </si>
   <si>
     <t>Öv</t>
+  </si>
+  <si>
+    <t>Oda-vissza ugyanaz</t>
+  </si>
+  <si>
+    <t>Sas</t>
+  </si>
+  <si>
+    <t>___ + LÁB</t>
+  </si>
+  <si>
+    <t>Kamat</t>
   </si>
 </sst>
 </file>
@@ -1449,21 +1461,21 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1484,25 +1496,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1544,6 +1550,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1551,9 +1560,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1639,6 +1645,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2821,13 +2831,13 @@
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>187</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>189</v>
@@ -2849,16 +2859,16 @@
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>193</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J31" s="5"/>
     </row>
@@ -2873,20 +2883,20 @@
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>195</v>
+        <v>464</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>199</v>
+        <v>465</v>
       </c>
       <c r="J32" s="5"/>
     </row>
@@ -2901,20 +2911,20 @@
         <v>4</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>200</v>
+        <v>466</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>203</v>
+        <v>467</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>204</v>
+        <v>141</v>
       </c>
       <c r="J33" s="5"/>
     </row>
@@ -8213,7 +8223,11 @@
         <v>457</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>50</v>
+        <v>183</v>
+      </c>
+      <c r="C2" t="str">
+        <f>VLOOKUP(B2,Feladványok!A:B,2,FALSE)</f>
+        <v>2026-10-01</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -8222,75 +8236,75 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="str">
+      <c r="A6" s="10" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+1-1)</f>
-        <v>Ikrek</v>
+        <v>Indián</v>
       </c>
       <c r="B6" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+2-1)</f>
-        <v>Puli</v>
-      </c>
-      <c r="C6" s="9" t="str">
+        <v>Szék</v>
+      </c>
+      <c r="C6" s="8" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+3-1)</f>
-        <v>Csat</v>
-      </c>
-      <c r="D6" s="10" t="str">
+        <v>Kapor</v>
+      </c>
+      <c r="D6" s="8" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+4-1)</f>
-        <v>Rest</v>
+        <v>Csend</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="8" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+5-1)</f>
-        <v>Pumi</v>
-      </c>
-      <c r="B7" s="8" t="str">
+        <v>Görög</v>
+      </c>
+      <c r="B7" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+6-1)</f>
-        <v>Bika</v>
-      </c>
-      <c r="C7" s="8" t="str">
+        <v>Kerek</v>
+      </c>
+      <c r="C7" s="10" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+7-1)</f>
-        <v>Rák</v>
-      </c>
-      <c r="D7" s="9" t="str">
+        <v>Bors</v>
+      </c>
+      <c r="D7" s="10" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+8-1)</f>
-        <v>Cipő</v>
+        <v>Vihar</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="str">
+      <c r="A8" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+9-1)</f>
-        <v>Bélés</v>
-      </c>
-      <c r="B8" s="10" t="str">
+        <v>Pap</v>
+      </c>
+      <c r="B8" s="9" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+10-1)</f>
-        <v>Volna</v>
-      </c>
-      <c r="C8" s="9" t="str">
+        <v>Kömény</v>
+      </c>
+      <c r="C8" s="8" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+11-1)</f>
-        <v>Mérleg</v>
-      </c>
-      <c r="D8" s="7" t="str">
+        <v>Gomba</v>
+      </c>
+      <c r="D8" s="9" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+12-1)</f>
-        <v>Vizsla</v>
+        <v>Kakas</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="str">
+      <c r="A9" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+13-1)</f>
-        <v>Fehér</v>
-      </c>
-      <c r="B9" s="8" t="str">
+        <v>Babér</v>
+      </c>
+      <c r="B9" s="9" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+14-1)</f>
-        <v>Kos</v>
+        <v>Malom</v>
       </c>
       <c r="C9" s="9" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+15-1)</f>
-        <v>Harang</v>
-      </c>
-      <c r="D9" s="7" t="str">
+        <v>Asztal</v>
+      </c>
+      <c r="D9" s="10" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+16-1)</f>
-        <v>Kuvasz</v>
+        <v>Nadrág</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -8321,23 +8335,23 @@
       </c>
       <c r="B23" s="5" t="str">
         <f>INDEX(Feladványok!$D$2:$D$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Csillagjegyek</v>
+        <v>Fűszerek</v>
       </c>
       <c r="C23" s="5" t="str">
         <f>INDEX(Feladványok!$F$2:$F$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Rák</v>
+        <v>Kömény</v>
       </c>
       <c r="D23" s="5" t="str">
         <f>INDEX(Feladványok!$G$2:$G$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Kos</v>
+        <v>Bors</v>
       </c>
       <c r="E23" s="5" t="str">
         <f>INDEX(Feladványok!$H$2:$H$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Bika</v>
+        <v>Kapor</v>
       </c>
       <c r="F23" s="5" t="str">
         <f>INDEX(Feladványok!$I$2:$I$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Ikrek</v>
+        <v>Babér</v>
       </c>
       <c r="G23" s="5" t="str">
         <f>IF(INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)="","",INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1))</f>
@@ -8350,23 +8364,23 @@
       </c>
       <c r="B24" s="5" t="str">
         <f>INDEX(Feladványok!$D$2:$D$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>Magyar kutyafajták</v>
+        <v>SZÉL + ___</v>
       </c>
       <c r="C24" s="5" t="str">
         <f>INDEX(Feladványok!$F$2:$F$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>Puli</v>
+        <v>Malom</v>
       </c>
       <c r="D24" s="5" t="str">
         <f>INDEX(Feladványok!$G$2:$G$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>Vizsla</v>
+        <v>Csend</v>
       </c>
       <c r="E24" s="5" t="str">
         <f>INDEX(Feladványok!$H$2:$H$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>Kuvasz</v>
+        <v>Kakas</v>
       </c>
       <c r="F24" s="5" t="str">
         <f>INDEX(Feladványok!$I$2:$I$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>Pumi</v>
+        <v>Vihar</v>
       </c>
       <c r="G24" s="5" t="str">
         <f>IF(INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)="","",INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1))</f>
@@ -8379,23 +8393,23 @@
       </c>
       <c r="B25" s="5" t="str">
         <f>INDEX(Feladványok!$D$2:$D$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Aminek nyelve van</v>
+        <v>Aminek lába van</v>
       </c>
       <c r="C25" s="5" t="str">
         <f>INDEX(Feladványok!$F$2:$F$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Cipő</v>
+        <v>Asztal</v>
       </c>
       <c r="D25" s="5" t="str">
         <f>INDEX(Feladványok!$G$2:$G$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Harang</v>
+        <v>Gomba</v>
       </c>
       <c r="E25" s="5" t="str">
         <f>INDEX(Feladványok!$H$2:$H$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Öv</v>
+        <v>Nadrág</v>
       </c>
       <c r="F25" s="5" t="str">
         <f>INDEX(Feladványok!$I$2:$I$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Mérleg</v>
+        <v>Szék</v>
       </c>
       <c r="G25" s="5" t="str">
         <f>IF(INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)="","",INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1))</f>
@@ -8408,27 +8422,27 @@
       </c>
       <c r="B26" s="5" t="str">
         <f>INDEX(Feladványok!$D$2:$D$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Egy betű cseréjével vármegye</v>
+        <v>Palindrom szavak</v>
       </c>
       <c r="C26" s="5" t="str">
         <f>INDEX(Feladványok!$F$2:$F$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Fehér</v>
+        <v>Görög</v>
       </c>
       <c r="D26" s="5" t="str">
         <f>INDEX(Feladványok!$G$2:$G$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Bélés</v>
+        <v>Indián</v>
       </c>
       <c r="E26" s="5" t="str">
         <f>INDEX(Feladványok!$H$2:$H$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Rest</v>
+        <v>Kerek</v>
       </c>
       <c r="F26" s="5" t="str">
         <f>INDEX(Feladványok!$I$2:$I$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Volna</v>
+        <v>Pap</v>
       </c>
       <c r="G26" s="5" t="str">
         <f>IF(INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)="","",INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1))</f>
-        <v>Fejér, Békés, Pest, Tolna</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/feladvanyok.xlsx
+++ b/feladvanyok.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a3b2d023d0b90a2/Dokumentumok/GitHub/rokonszavak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_4BC928A0A355CC1831E4553E7CBF07CDD619E1D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{628C337C-280F-4B15-A767-E1BC83D40D2F}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_4BC928A0A355CC1831E4553E7CBF07CDD619E1D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{885B2CDE-6310-4B00-964D-4E043AFEDFFA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Segéd" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="Játék" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="466">
   <si>
     <t>Rokonszavak – feladványbank és gyakorlólap</t>
   </si>
@@ -626,9 +626,6 @@
     <t>Vihar</t>
   </si>
   <si>
-    <t>Aminek lába van</t>
-  </si>
-  <si>
     <t>Asztal</t>
   </si>
   <si>
@@ -639,9 +636,6 @@
   </si>
   <si>
     <t>Szék</t>
-  </si>
-  <si>
-    <t>Palindrom szavak</t>
   </si>
   <si>
     <t>Görög</t>
@@ -1475,7 +1469,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1496,19 +1490,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1540,7 +1522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1554,12 +1536,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1645,10 +1621,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2207,7 +2179,7 @@
         <v>64</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>66</v>
@@ -2883,20 +2855,20 @@
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>203</v>
-      </c>
       <c r="H32" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J32" s="5"/>
     </row>
@@ -2911,17 +2883,17 @@
         <v>4</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>141</v>
@@ -2930,1019 +2902,1021 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C34" s="5">
         <v>1</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="I34" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="J34" s="5"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C35" s="5">
         <v>2</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="I35" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="J35" s="5"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C36" s="5">
         <v>3</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="I36" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C37" s="5">
         <v>4</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="J37" s="5"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C38" s="5">
         <v>1</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="I38" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>233</v>
       </c>
       <c r="J38" s="5"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C39" s="5">
         <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="I39" s="5" t="s">
         <v>236</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>238</v>
       </c>
       <c r="J39" s="5"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C40" s="5">
         <v>3</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="I40" s="5" t="s">
         <v>241</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>243</v>
       </c>
       <c r="J40" s="5"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C41" s="5">
         <v>4</v>
       </c>
       <c r="D41" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="H41" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="I41" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>249</v>
       </c>
       <c r="J41" s="5"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C42" s="5">
         <v>1</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H42" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="I42" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="J42" s="5"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C43" s="5">
         <v>2</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G43" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Csap</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>261</v>
       </c>
       <c r="J43" s="5"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C44" s="5">
         <v>3</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="I44" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>266</v>
       </c>
       <c r="J44" s="5"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C45" s="5">
         <v>4</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="H45" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="I45" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="J45" s="5" t="s">
         <v>270</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C46" s="5">
         <v>1</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="I46" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="J46" s="5"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C47" s="5">
         <v>2</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="I47" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>284</v>
       </c>
       <c r="J47" s="5"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C48" s="5">
         <v>3</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H48" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="I48" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>289</v>
       </c>
       <c r="J48" s="5"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C49" s="5">
         <v>4</v>
       </c>
       <c r="D49" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="G49" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="H49" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="I49" s="5" t="s">
         <v>293</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>295</v>
       </c>
       <c r="J49" s="5"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C50" s="5">
         <v>1</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="H50" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="I50" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>302</v>
       </c>
       <c r="J50" s="5"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C51" s="5">
         <v>2</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="H51" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="I51" s="5" t="s">
         <v>305</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>307</v>
       </c>
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C52" s="5">
         <v>3</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="H52" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="I52" s="5" t="s">
         <v>310</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>312</v>
       </c>
       <c r="J52" s="5"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C53" s="5">
         <v>4</v>
       </c>
       <c r="D53" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="G53" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="H53" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="I53" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="J53" s="5" t="s">
         <v>317</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C54" s="5">
         <v>1</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="H54" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="I54" s="5" t="s">
         <v>324</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>326</v>
       </c>
       <c r="J54" s="5"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C55" s="5">
         <v>2</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H55" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="G55" s="5" t="s">
+      <c r="I55" s="5" t="s">
         <v>329</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>331</v>
       </c>
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C56" s="5">
         <v>3</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="H56" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="I56" s="5" t="s">
         <v>334</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>336</v>
       </c>
       <c r="J56" s="5"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C57" s="5">
         <v>4</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="H57" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="I57" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="J57" s="5"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C58" s="5">
         <v>1</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H58" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="I58" s="5" t="s">
         <v>346</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="J58" s="5"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C59" s="5">
         <v>2</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H59" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="I59" s="5" t="s">
         <v>351</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="J59" s="5"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C60" s="5">
         <v>3</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H60" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="I60" s="5" t="s">
         <v>356</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>358</v>
       </c>
       <c r="J60" s="5"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C61" s="5">
         <v>4</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="G61" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="H61" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="I61" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="H61" s="5" t="s">
+      <c r="J61" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C62" s="5">
         <v>1</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="H62" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="I62" s="5" t="s">
         <v>370</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>372</v>
       </c>
       <c r="J62" s="5"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C63" s="5">
         <v>2</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="H63" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="I63" s="5" t="s">
         <v>375</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>377</v>
       </c>
       <c r="J63" s="5"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C64" s="5">
         <v>3</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H64" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="I64" s="5" t="s">
         <v>380</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>382</v>
       </c>
       <c r="J64" s="5"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C65" s="5">
         <v>4</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="G65" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="H65" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="G65" s="5" t="s">
+      <c r="I65" s="5" t="s">
         <v>386</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>388</v>
       </c>
       <c r="J65" s="5"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C66" s="5">
         <v>1</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="H66" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="I66" s="5" t="s">
         <v>393</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>395</v>
       </c>
       <c r="J66" s="5"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C67" s="5">
         <v>2</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G67" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="I67" s="5" t="s">
         <v>397</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>399</v>
       </c>
       <c r="J67" s="5"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C68" s="5">
         <v>3</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H68" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="I68" s="5" t="s">
         <v>402</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>404</v>
       </c>
       <c r="J68" s="5"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C69" s="5">
         <v>4</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>35</v>
@@ -3954,230 +3928,230 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C70" s="5">
         <v>1</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="H70" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="I70" s="5" t="s">
         <v>412</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>414</v>
       </c>
       <c r="J70" s="5"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C71" s="5">
         <v>2</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="H71" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="G71" s="5" t="s">
+      <c r="I71" s="5" t="s">
         <v>417</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>419</v>
       </c>
       <c r="J71" s="5"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C72" s="5">
         <v>3</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="H72" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="I72" s="5" t="s">
         <v>422</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="I72" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="J72" s="5"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C73" s="5">
         <v>4</v>
       </c>
       <c r="D73" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F73" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="G73" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="H73" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>429</v>
-      </c>
       <c r="I73" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J73" s="5"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C74" s="5">
         <v>1</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="H74" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="I74" s="5" t="s">
         <v>434</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="I74" s="5" t="s">
-        <v>436</v>
       </c>
       <c r="J74" s="5"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C75" s="5">
         <v>2</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="H75" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="G75" s="5" t="s">
+      <c r="I75" s="5" t="s">
         <v>439</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>441</v>
       </c>
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C76" s="5">
         <v>3</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="H76" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="I76" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>446</v>
       </c>
       <c r="J76" s="5"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C77" s="5">
         <v>4</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="H77" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="I77" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="H77" s="5" t="s">
+      <c r="J77" s="5" t="s">
         <v>450</v>
-      </c>
-      <c r="I77" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="J77" s="5" t="s">
-        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -4196,14 +4170,14 @@
         <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -4338,7 +4312,7 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -4353,7 +4327,7 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -4368,7 +4342,7 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -4383,7 +4357,7 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -4398,7 +4372,7 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -4413,7 +4387,7 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -4428,7 +4402,7 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -4443,7 +4417,7 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -4458,7 +4432,7 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -4473,7 +4447,7 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -4488,7 +4462,7 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -5708,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
@@ -5721,7 +5695,7 @@
         <v>2</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
@@ -5760,7 +5734,7 @@
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
@@ -5773,7 +5747,7 @@
         <v>6</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
@@ -5812,7 +5786,7 @@
         <v>9</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
@@ -5838,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
@@ -5890,7 +5864,7 @@
         <v>15</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
@@ -5903,1691 +5877,1691 @@
         <v>16</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B130" s="2">
         <v>1</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B131" s="2">
         <v>2</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B132" s="2">
         <v>3</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B133" s="2">
         <v>4</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B134" s="2">
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B135" s="2">
         <v>6</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B136" s="2">
         <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B137" s="2">
         <v>8</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B138" s="2">
         <v>9</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B139" s="2">
         <v>10</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B140" s="2">
         <v>11</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B141" s="2">
         <v>12</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B142" s="2">
         <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B143" s="2">
         <v>14</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B144" s="2">
         <v>15</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B145" s="2">
         <v>16</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B146" s="2">
         <v>1</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B147" s="2">
         <v>2</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B148" s="2">
         <v>3</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B149" s="2">
         <v>4</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B150" s="2">
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B151" s="2">
         <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B152" s="2">
         <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B153" s="2">
         <v>8</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B154" s="2">
         <v>9</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B155" s="2">
         <v>10</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B156" s="2">
         <v>11</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B157" s="2">
         <v>12</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B158" s="2">
         <v>13</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B159" s="2">
         <v>14</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B160" s="2">
         <v>15</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B161" s="2">
         <v>16</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B162" s="2">
         <v>1</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B163" s="2">
         <v>2</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B164" s="2">
         <v>3</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B165" s="2">
         <v>4</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B166" s="2">
         <v>5</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B167" s="2">
         <v>6</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B168" s="2">
         <v>7</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B169" s="2">
         <v>8</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B170" s="2">
         <v>9</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B171" s="2">
         <v>10</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B172" s="2">
         <v>11</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B173" s="2">
         <v>12</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B174" s="2">
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B175" s="2">
         <v>14</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B176" s="2">
         <v>15</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B177" s="2">
         <v>16</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B178" s="2">
         <v>1</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B179" s="2">
         <v>2</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B180" s="2">
         <v>3</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B181" s="2">
         <v>4</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B182" s="2">
         <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B183" s="2">
         <v>6</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B184" s="2">
         <v>7</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B185" s="2">
         <v>8</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B186" s="2">
         <v>9</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B187" s="2">
         <v>10</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B188" s="2">
         <v>11</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B189" s="2">
         <v>12</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B190" s="2">
         <v>13</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B191" s="2">
         <v>14</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B192" s="2">
         <v>15</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B193" s="2">
         <v>16</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B194" s="2">
         <v>1</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B195" s="2">
         <v>2</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B196" s="2">
         <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B197" s="2">
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B198" s="2">
         <v>5</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B199" s="2">
         <v>6</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B200" s="2">
         <v>7</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B201" s="2">
         <v>8</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B202" s="2">
         <v>9</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B203" s="2">
         <v>10</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B204" s="2">
         <v>11</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B205" s="2">
         <v>12</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B206" s="2">
         <v>13</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B207" s="2">
         <v>14</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B208" s="2">
         <v>15</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B209" s="2">
         <v>16</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B210" s="2">
         <v>1</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B211" s="2">
         <v>2</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B212" s="2">
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B213" s="2">
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B214" s="2">
         <v>5</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B215" s="2">
         <v>6</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B216" s="2">
         <v>7</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B217" s="2">
         <v>8</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B218" s="2">
         <v>9</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B219" s="2">
         <v>10</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B220" s="2">
         <v>11</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B221" s="2">
         <v>12</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B222" s="2">
         <v>13</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B223" s="2">
         <v>14</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B224" s="2">
         <v>15</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B225" s="2">
         <v>16</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B226" s="2">
         <v>1</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B227" s="2">
         <v>2</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B228" s="2">
         <v>3</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B229" s="2">
         <v>4</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B230" s="2">
         <v>5</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B231" s="2">
         <v>6</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B232" s="2">
         <v>7</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B233" s="2">
         <v>8</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B234" s="2">
         <v>9</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B235" s="2">
         <v>10</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B236" s="2">
         <v>11</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B237" s="2">
         <v>12</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B238" s="2">
         <v>13</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B239" s="2">
         <v>14</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B240" s="2">
         <v>15</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B241" s="2">
         <v>16</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" s="2"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B242" s="2">
         <v>1</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" s="2"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B243" s="2">
         <v>2</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" s="2"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B244" s="2">
         <v>3</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" s="2"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B245" s="2">
         <v>4</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" s="2"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B246" s="2">
         <v>5</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" s="2"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B247" s="2">
         <v>6</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B248" s="2">
         <v>7</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B249" s="2">
         <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B250" s="2">
         <v>9</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B251" s="2">
         <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D251" s="2"/>
       <c r="E251" s="2"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B252" s="2">
         <v>11</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D252" s="2"/>
       <c r="E252" s="2"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B253" s="2">
         <v>12</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" s="2"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B254" s="2">
         <v>13</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" s="2"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B255" s="2">
         <v>14</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B256" s="2">
         <v>15</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D256" s="2"/>
       <c r="E256" s="2"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B257" s="2">
         <v>16</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" s="2"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B258" s="2">
         <v>1</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D258" s="2"/>
       <c r="E258" s="2"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B259" s="2">
         <v>2</v>
@@ -7600,124 +7574,124 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B260" s="2">
         <v>3</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" s="2"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B261" s="2">
         <v>4</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" s="2"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B262" s="2">
         <v>5</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B263" s="2">
         <v>6</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D263" s="2"/>
       <c r="E263" s="2"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B264" s="2">
         <v>7</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D264" s="2"/>
       <c r="E264" s="2"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B265" s="2">
         <v>8</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D265" s="2"/>
       <c r="E265" s="2"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B266" s="2">
         <v>9</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D266" s="2"/>
       <c r="E266" s="2"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B267" s="2">
         <v>10</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B268" s="2">
         <v>11</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D268" s="2"/>
       <c r="E268" s="2"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B269" s="2">
         <v>12</v>
@@ -7730,468 +7704,468 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B270" s="2">
         <v>13</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D270" s="2"/>
       <c r="E270" s="2"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B271" s="2">
         <v>14</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D271" s="2"/>
       <c r="E271" s="2"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B272" s="2">
         <v>15</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D272" s="2"/>
       <c r="E272" s="2"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B273" s="2">
         <v>16</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D273" s="2"/>
       <c r="E273" s="2"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B274" s="2">
         <v>1</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" s="2"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B275" s="2">
         <v>2</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" s="2"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B276" s="2">
         <v>3</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B277" s="2">
         <v>4</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" s="2"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B278" s="2">
         <v>5</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B279" s="2">
         <v>6</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" s="2"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B280" s="2">
         <v>7</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" s="2"/>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B281" s="2">
         <v>8</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" s="2"/>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B282" s="2">
         <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" s="2"/>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B283" s="2">
         <v>10</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B284" s="2">
         <v>11</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B285" s="2">
         <v>12</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B286" s="2">
         <v>13</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" s="2"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B287" s="2">
         <v>14</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B288" s="2">
         <v>15</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B289" s="2">
         <v>16</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B290" s="2">
         <v>1</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" s="2"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B291" s="2">
         <v>2</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" s="2"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B292" s="2">
         <v>3</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" s="2"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B293" s="2">
         <v>4</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" s="2"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B294" s="2">
         <v>5</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" s="2"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B295" s="2">
         <v>6</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" s="2"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B296" s="2">
         <v>7</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" s="2"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B297" s="2">
         <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" s="2"/>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B298" s="2">
         <v>9</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B299" s="2">
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" s="2"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B300" s="2">
         <v>11</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" s="2"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B301" s="2">
         <v>12</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" s="2"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B302" s="2">
         <v>13</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" s="2"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B303" s="2">
         <v>14</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B304" s="2">
         <v>15</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" s="2"/>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B305" s="2">
         <v>16</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
@@ -8215,118 +8189,118 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>183</v>
+        <v>248</v>
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP(B2,Feladványok!A:B,2,FALSE)</f>
-        <v>2026-10-01</v>
+        <v>2026-10-04</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="str">
+      <c r="A6" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+1-1)</f>
-        <v>Indián</v>
+        <v>Fog</v>
       </c>
       <c r="B6" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+2-1)</f>
-        <v>Szék</v>
+        <v>Kő</v>
       </c>
       <c r="C6" s="8" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+3-1)</f>
-        <v>Kapor</v>
-      </c>
-      <c r="D6" s="8" t="str">
+        <v>Csuka</v>
+      </c>
+      <c r="D6" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+4-1)</f>
-        <v>Csend</v>
+        <v>Ponty</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="str">
+      <c r="A7" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+5-1)</f>
-        <v>Görög</v>
+        <v>Keszeg</v>
       </c>
       <c r="B7" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+6-1)</f>
-        <v>Kerek</v>
-      </c>
-      <c r="C7" s="10" t="str">
+        <v>Veszély</v>
+      </c>
+      <c r="C7" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+7-1)</f>
-        <v>Bors</v>
-      </c>
-      <c r="D7" s="10" t="str">
+        <v>Fal</v>
+      </c>
+      <c r="D7" s="8" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+8-1)</f>
-        <v>Vihar</v>
+        <v>Vár</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="8" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+9-1)</f>
-        <v>Pap</v>
-      </c>
-      <c r="B8" s="9" t="str">
+        <v>Ég</v>
+      </c>
+      <c r="B8" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+10-1)</f>
-        <v>Kömény</v>
-      </c>
-      <c r="C8" s="8" t="str">
+        <v>Cipzár</v>
+      </c>
+      <c r="C8" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+11-1)</f>
-        <v>Gomba</v>
-      </c>
-      <c r="D8" s="9" t="str">
+        <v>Harcsa</v>
+      </c>
+      <c r="D8" s="8" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+12-1)</f>
-        <v>Kakas</v>
+        <v>Fésű</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+13-1)</f>
-        <v>Babér</v>
-      </c>
-      <c r="B9" s="9" t="str">
+        <v>Oltó</v>
+      </c>
+      <c r="B9" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+14-1)</f>
-        <v>Malom</v>
-      </c>
-      <c r="C9" s="9" t="str">
+        <v>Fűrész</v>
+      </c>
+      <c r="C9" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+15-1)</f>
-        <v>Asztal</v>
-      </c>
-      <c r="D9" s="10" t="str">
+        <v>Gereblye</v>
+      </c>
+      <c r="D9" s="7" t="str">
         <f>INDEX(Segéd!$C$2:$C$305,MATCH($B$2,Segéd!$A$2:$A$305,0)+16-1)</f>
-        <v>Nadrág</v>
+        <v>Nyúl</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -8335,23 +8309,23 @@
       </c>
       <c r="B23" s="5" t="str">
         <f>INDEX(Feladványok!$D$2:$D$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Fűszerek</v>
+        <v>Halak</v>
       </c>
       <c r="C23" s="5" t="str">
         <f>INDEX(Feladványok!$F$2:$F$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Kömény</v>
+        <v>Ponty</v>
       </c>
       <c r="D23" s="5" t="str">
         <f>INDEX(Feladványok!$G$2:$G$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Bors</v>
+        <v>Harcsa</v>
       </c>
       <c r="E23" s="5" t="str">
         <f>INDEX(Feladványok!$H$2:$H$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Kapor</v>
+        <v>Keszeg</v>
       </c>
       <c r="F23" s="5" t="str">
         <f>INDEX(Feladványok!$I$2:$I$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)</f>
-        <v>Babér</v>
+        <v>Csuka</v>
       </c>
       <c r="G23" s="5" t="str">
         <f>IF(INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1)="","",INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+1-1))</f>
@@ -8364,23 +8338,23 @@
       </c>
       <c r="B24" s="5" t="str">
         <f>INDEX(Feladványok!$D$2:$D$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>SZÉL + ___</v>
+        <v>TŰZ + ___</v>
       </c>
       <c r="C24" s="5" t="str">
         <f>INDEX(Feladványok!$F$2:$F$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>Malom</v>
+        <v>Oltó</v>
       </c>
       <c r="D24" s="5" t="str">
         <f>INDEX(Feladványok!$G$2:$G$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>Csend</v>
+        <v>Fal</v>
       </c>
       <c r="E24" s="5" t="str">
         <f>INDEX(Feladványok!$H$2:$H$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>Kakas</v>
+        <v>Kő</v>
       </c>
       <c r="F24" s="5" t="str">
         <f>INDEX(Feladványok!$I$2:$I$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)</f>
-        <v>Vihar</v>
+        <v>Veszély</v>
       </c>
       <c r="G24" s="5" t="str">
         <f>IF(INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1)="","",INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+2-1))</f>
@@ -8393,23 +8367,23 @@
       </c>
       <c r="B25" s="5" t="str">
         <f>INDEX(Feladványok!$D$2:$D$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Aminek lába van</v>
+        <v>Aminek foga van</v>
       </c>
       <c r="C25" s="5" t="str">
         <f>INDEX(Feladványok!$F$2:$F$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Asztal</v>
+        <v>Fésű</v>
       </c>
       <c r="D25" s="5" t="str">
         <f>INDEX(Feladványok!$G$2:$G$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Gomba</v>
+        <v>Fűrész</v>
       </c>
       <c r="E25" s="5" t="str">
         <f>INDEX(Feladványok!$H$2:$H$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Nadrág</v>
+        <v>Gereblye</v>
       </c>
       <c r="F25" s="5" t="str">
         <f>INDEX(Feladványok!$I$2:$I$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)</f>
-        <v>Szék</v>
+        <v>Cipzár</v>
       </c>
       <c r="G25" s="5" t="str">
         <f>IF(INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1)="","",INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+3-1))</f>
@@ -8422,23 +8396,23 @@
       </c>
       <c r="B26" s="5" t="str">
         <f>INDEX(Feladványok!$D$2:$D$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Palindrom szavak</v>
+        <v>Főnév és ige is egyben</v>
       </c>
       <c r="C26" s="5" t="str">
         <f>INDEX(Feladványok!$F$2:$F$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Görög</v>
+        <v>Vár</v>
       </c>
       <c r="D26" s="5" t="str">
         <f>INDEX(Feladványok!$G$2:$G$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Indián</v>
+        <v>Fog</v>
       </c>
       <c r="E26" s="5" t="str">
         <f>INDEX(Feladványok!$H$2:$H$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Kerek</v>
+        <v>Nyúl</v>
       </c>
       <c r="F26" s="5" t="str">
         <f>INDEX(Feladványok!$I$2:$I$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)</f>
-        <v>Pap</v>
+        <v>Ég</v>
       </c>
       <c r="G26" s="5" t="str">
         <f>IF(INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1)="","",INDEX(Feladványok!$E$2:$E$77,MATCH($B$2,Feladványok!$A$2:$A$77,0)+4-1))</f>

--- a/feladvanyok.xlsx
+++ b/feladvanyok.xlsx
@@ -1702,7 +1702,7 @@
     <t xml:space="preserve">Ország rejtőzik a szóban</t>
   </si>
   <si>
-    <t xml:space="preserve">Kína, Irán, India, Mali</t>
+    <t xml:space="preserve">Kína, Irán, India, Omán</t>
   </si>
   <si>
     <t xml:space="preserve">Kínál</t>
@@ -1714,7 +1714,7 @@
     <t xml:space="preserve">Indián</t>
   </si>
   <si>
-    <t xml:space="preserve">Malária</t>
+    <t xml:space="preserve">Románc</t>
   </si>
   <si>
     <t xml:space="preserve">rsz-001</t>

--- a/feladvanyok.xlsx
+++ b/feladvanyok.xlsx
@@ -6318,7 +6318,7 @@
         <v>100</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="J112" s="7"/>
       <c r="K112" s="8" t="s">

--- a/feladvanyok.xlsx
+++ b/feladvanyok.xlsx
@@ -11,15 +11,19 @@
     <sheet name="Segéd" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="Játék" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="feladvany_lista">'Segéd'!$E$2:$E$43</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -57,6 +61,9 @@
       <family val="2"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -112,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,6 +141,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -395,7 +406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -500,6 +511,55 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>ÚJ SZABÁLY: egy csoporton belül ne végződjön három szó ugyanúgy (pl. mind -usz vagy mind -on). A közös végződés ránézésre megadja a csoportot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>ÚJ SZABÁLY: ne legyen sok tulajdonneves csoport, és ritkán térjen vissza az "amit lehet X-ni" meg a "___ + SZÓ" típus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>A megjegyzes oszlopba csak akkor írj, ha tényleg hoz új infót (teljes név, rövidítés feloldása, ritka szó jelentése). Ami a kategórianévből amúgy is kiderül, azt hagyd üresen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-24: 10 új feladvány (rsz-033 – rsz-042).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>A Játék lap B2 cellája legördülő lista lett. Új feladvány után bővítsd a Segéd lap E oszlopát és a feladvany_lista nevet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Javítva: a Játék lap képlettartományai csak 24 feladványig értek; az A7 cella az 1. szót ismételte az 5. helyett.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Figyelem: rsz-040 "Terjedelem" szava 10 karakter - kétsoros doboz kell hozzá.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -513,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -589,7 +649,7 @@
           <t>rsz-002</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
@@ -6432,6 +6492,1850 @@
       <c r="K129" s="8" t="inlineStr">
         <is>
           <t>Mérföld mértékegységnek látszik, de nem űrmérték. Egyik szó sem illik valóban más csoportba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>Katonai rangok</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>Tizedes</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>Őrmester</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>Hadnagy</t>
+        </is>
+      </c>
+      <c r="I130" s="7" t="inlineStr">
+        <is>
+          <t>Zászlós</t>
+        </is>
+      </c>
+      <c r="J130" s="7" t="n"/>
+      <c r="K130" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport. A Tizedes tizedes tört is, a Zászlós melléknévnek hat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B131" s="14" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C131" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>Bányászati fogalmak</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>A csille a bányában használt kisvasúti kocsi</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Tárna</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>Vágat</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>Csille</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="inlineStr">
+        <is>
+          <t>Fejtés</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="n"/>
+      <c r="K131" s="8" t="inlineStr">
+        <is>
+          <t>A Fejtés rejtvényfejtés is, a Vágat a vág igére hajaz. A 3. csoporttal közös a föld alatti közeg - ez a csapda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>Földtörténeti korok</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="n"/>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>Jura</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>Kréta</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>Triász</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="inlineStr">
+        <is>
+          <t>Perm</t>
+        </is>
+      </c>
+      <c r="J132" s="7" t="n"/>
+      <c r="K132" s="8" t="inlineStr">
+        <is>
+          <t>FŐ CSAPDA: Kréta = rajzeszköz és görög sziget, Jura = hegység, Perm = orosz város.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C133" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>___ + PONT</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>fagypont, súlypont, támpont, végpont</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Fagy</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Súly</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>Tám</t>
+        </is>
+      </c>
+      <c r="I133" s="7" t="inlineStr">
+        <is>
+          <t>Vég</t>
+        </is>
+      </c>
+      <c r="J133" s="7" t="n"/>
+      <c r="K133" s="8" t="inlineStr">
+        <is>
+          <t>A Tám önmagában ritka szó, ez segít megfejteni. Ez az egyetlen összetételes csoport a tíz feladványban.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C134" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>Lombhullató fák</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="n"/>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>Tölgy</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>Bükk</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>Nyír</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="inlineStr">
+        <is>
+          <t>Juhar</t>
+        </is>
+      </c>
+      <c r="J134" s="7" t="n"/>
+      <c r="K134" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport. Bükk hegység is, Nyír ige is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C135" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>Zenei hangközök</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="n"/>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Kvint</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Oktáv</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>Terc</t>
+        </is>
+      </c>
+      <c r="I135" s="7" t="inlineStr">
+        <is>
+          <t>Szekund</t>
+        </is>
+      </c>
+      <c r="J135" s="7" t="n"/>
+      <c r="K135" s="8" t="inlineStr">
+        <is>
+          <t>Tudásigényes, de iskolai anyag. A Szekund a szekundál igére emlékeztet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C136" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>A gomba részei</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="n"/>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>Kalap</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>Tönk</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>Lemez</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="inlineStr">
+        <is>
+          <t>Spóra</t>
+        </is>
+      </c>
+      <c r="J136" s="7" t="n"/>
+      <c r="K136" s="8" t="inlineStr">
+        <is>
+          <t>CSAPDA: a Lemez hanglemez is, ezért a 2. csoport felé húz. A gombalemez viszont valódi gombarész.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B137" s="14" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C137" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>Rendszertani kategóriák</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="n"/>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>Faj</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>Nem</t>
+        </is>
+      </c>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>Rend</t>
+        </is>
+      </c>
+      <c r="I137" s="7" t="inlineStr">
+        <is>
+          <t>Osztály</t>
+        </is>
+      </c>
+      <c r="J137" s="7" t="n"/>
+      <c r="K137" s="8" t="inlineStr">
+        <is>
+          <t>A feladvány lelke: négy teljesen hétköznapi szó. A Nem tagadószó, a Rend és az Osztály iskolai fogalom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C138" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>Időjárási jelenségek</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="n"/>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>Zivatar</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>Dér</t>
+        </is>
+      </c>
+      <c r="H138" s="7" t="inlineStr">
+        <is>
+          <t>Jégeső</t>
+        </is>
+      </c>
+      <c r="I138" s="7" t="inlineStr">
+        <is>
+          <t>Köd</t>
+        </is>
+      </c>
+      <c r="J138" s="7" t="n"/>
+      <c r="K138" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B139" s="14" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>Szövetfajták</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="n"/>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>Bársony</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>Selyem</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>Vászon</t>
+        </is>
+      </c>
+      <c r="I139" s="7" t="inlineStr">
+        <is>
+          <t>Flanel</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="n"/>
+      <c r="K139" s="8" t="inlineStr">
+        <is>
+          <t>A Vászon mozivászon is, a Selyem a selymes szóra hajaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>Magyar Nobel-díjasok</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>Gábor Dénes, Wigner Jenő, Oláh György, Kertész Imre</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>Gábor</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>Wigner</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>Oláh</t>
+        </is>
+      </c>
+      <c r="I140" s="7" t="inlineStr">
+        <is>
+          <t>Kertész</t>
+        </is>
+      </c>
+      <c r="J140" s="7" t="n"/>
+      <c r="K140" s="8" t="inlineStr">
+        <is>
+          <t>A Gábor keresztnév, a Kertész foglalkozás, az Oláh népnév is - egyik sem puszta vezetéknévnek látszik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B141" s="14" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C141" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>Magyar matematikusok</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>Erdős Pál, Bolyai János, Neumann János, Riesz Frigyes</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>Erdős</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>Bolyai</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>Neumann</t>
+        </is>
+      </c>
+      <c r="I141" s="7" t="inlineStr">
+        <is>
+          <t>Riesz</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="n"/>
+      <c r="K141" s="8" t="inlineStr">
+        <is>
+          <t>FŐ CSAPDA: nyolc magyar tudós egy táblán. A szétválasztás egyetlen ténye: matematikai Nobel-díj nem létezik, így e négy közül egyik sem kaphatott. Erdős melléknév is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C142" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>Ami a patikában található</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="n"/>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>Recept</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>Kenőcs</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t>Tabletta</t>
+        </is>
+      </c>
+      <c r="I142" s="7" t="inlineStr">
+        <is>
+          <t>Kúp</t>
+        </is>
+      </c>
+      <c r="J142" s="7" t="n"/>
+      <c r="K142" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport. Recept étel is, Kúp mértani test is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C143" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>Az agy részei</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>A híd az agytörzs egyik szakasza</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>Kisagy</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>Nyúltvelő</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>Híd</t>
+        </is>
+      </c>
+      <c r="I143" s="7" t="inlineStr">
+        <is>
+          <t>Talamusz</t>
+        </is>
+      </c>
+      <c r="J143" s="7" t="n"/>
+      <c r="K143" s="8" t="inlineStr">
+        <is>
+          <t>Csak egy szó tartalmazza az agy szót, így nem lehet ránézésre megfejteni. A Híd budapesti híd is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C144" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>Vitaminhiány okozta betegségek</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="n"/>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>Skorbut</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>Angolkór</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>Beriberi</t>
+        </is>
+      </c>
+      <c r="I144" s="7" t="inlineStr">
+        <is>
+          <t>Pellagra</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="n"/>
+      <c r="K144" s="8" t="inlineStr">
+        <is>
+          <t>Tudásigényes. Az 1. csoporttal közös az orvosi közeg, de egyik betegség sem patikaszer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B145" s="14" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>Régi pénzérmék</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="n"/>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>Fillér</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>Garas</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>Peták</t>
+        </is>
+      </c>
+      <c r="I145" s="7" t="inlineStr">
+        <is>
+          <t>Dukát</t>
+        </is>
+      </c>
+      <c r="J145" s="7" t="n"/>
+      <c r="K145" s="8" t="inlineStr">
+        <is>
+          <t>Tudásigényes. A Garas a garasoskodik igéből ismerős, a Fillér ma is él a szólásokban.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>Írásjelek</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="n"/>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>Vessző</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>Pont</t>
+        </is>
+      </c>
+      <c r="H146" s="7" t="inlineStr">
+        <is>
+          <t>Zárójel</t>
+        </is>
+      </c>
+      <c r="I146" s="7" t="inlineStr">
+        <is>
+          <t>Aposztróf</t>
+        </is>
+      </c>
+      <c r="J146" s="7" t="n"/>
+      <c r="K146" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport. Vessző fenyítőeszköz is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B147" s="14" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C147" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>Uralkodóházak</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="n"/>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>Árpád</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>Anjou</t>
+        </is>
+      </c>
+      <c r="H147" s="7" t="inlineStr">
+        <is>
+          <t>Habsburg</t>
+        </is>
+      </c>
+      <c r="I147" s="7" t="inlineStr">
+        <is>
+          <t>Jagelló</t>
+        </is>
+      </c>
+      <c r="J147" s="7" t="n"/>
+      <c r="K147" s="8" t="inlineStr">
+        <is>
+          <t>Nem névlista: a dinasztiát kell felismerni. Árpád keresztnév is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C148" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>Spanyolország nyelvei</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>A galego Galicia, az asztúr Asztúria nyelve</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>Baszk</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>Katalán</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>Galego</t>
+        </is>
+      </c>
+      <c r="I148" s="7" t="inlineStr">
+        <is>
+          <t>Asztúr</t>
+        </is>
+      </c>
+      <c r="J148" s="7" t="n"/>
+      <c r="K148" s="8" t="inlineStr">
+        <is>
+          <t>Tudásigényes. A Galego Galicia, az Asztúr Asztúria hivatalosan elismert nyelve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B149" s="14" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C149" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D149" s="8" t="inlineStr">
+        <is>
+          <t>Nyelvújítási szavak</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="n"/>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>Zongora</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>Rovar</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
+          <t>Évszak</t>
+        </is>
+      </c>
+      <c r="I149" s="7" t="inlineStr">
+        <is>
+          <t>Mérnök</t>
+        </is>
+      </c>
+      <c r="J149" s="7" t="n"/>
+      <c r="K149" s="8" t="inlineStr">
+        <is>
+          <t>FŐ CSAPDA: négy teljesen hétköznapi szó, amikről nem gondolná az ember, hogy mesterségesen gyártották őket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C150" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>Magyar tavak</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>Velencei-tó, Hévízi-tó, Fertő tó</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>Balaton</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>Velencei</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
+          <t>Fertő</t>
+        </is>
+      </c>
+      <c r="I150" s="7" t="inlineStr">
+        <is>
+          <t>Hévíz</t>
+        </is>
+      </c>
+      <c r="J150" s="7" t="n"/>
+      <c r="K150" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport. Fertő = mocsár, bűnös hely is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B151" s="14" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C151" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>Halmazállapotok</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="n"/>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>Szilárd</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>Folyékony</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
+          <t>Légnemű</t>
+        </is>
+      </c>
+      <c r="I151" s="7" t="inlineStr">
+        <is>
+          <t>Plazma</t>
+        </is>
+      </c>
+      <c r="J151" s="7" t="n"/>
+      <c r="K151" s="8" t="inlineStr">
+        <is>
+          <t>A Plazma vérplazma is, a Szilárd keresztnév is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C152" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>Szőlőfajták</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="n"/>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>Kadarka</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>Furmint</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
+          <t>Juhfark</t>
+        </is>
+      </c>
+      <c r="I152" s="7" t="inlineStr">
+        <is>
+          <t>Ezerjó</t>
+        </is>
+      </c>
+      <c r="J152" s="7" t="n"/>
+      <c r="K152" s="8" t="inlineStr">
+        <is>
+          <t>Tudásigényes. A Juhfark állatot, az Ezerjó dicséretet sejtet - ez a két szó viszi félre a játékost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>Magyar filmrendezők</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>Szabó István, Jancsó Miklós, Tarr Béla, Enyedi Ildikó</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>Szabó</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>Jancsó</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
+          <t>Tarr</t>
+        </is>
+      </c>
+      <c r="I153" s="7" t="inlineStr">
+        <is>
+          <t>Enyedi</t>
+        </is>
+      </c>
+      <c r="J153" s="7" t="n"/>
+      <c r="K153" s="8" t="inlineStr">
+        <is>
+          <t>A Szabó foglalkozás is, a Tarr a tar szóra hajaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="n">
+        <v>46326</v>
+      </c>
+      <c r="C154" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>Magyar népmesei alakok</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="n"/>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>Táltos</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>Tündér</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
+          <t>Óriás</t>
+        </is>
+      </c>
+      <c r="I154" s="7" t="inlineStr">
+        <is>
+          <t>Manó</t>
+        </is>
+      </c>
+      <c r="J154" s="7" t="n"/>
+      <c r="K154" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport. Sárkány szándékosan kimaradt: az csillagkép is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B155" s="14" t="n">
+        <v>46326</v>
+      </c>
+      <c r="C155" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>Középkori fegyverek</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="n"/>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>Buzogány</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>Szablya</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="inlineStr">
+        <is>
+          <t>Alabárd</t>
+        </is>
+      </c>
+      <c r="I155" s="7" t="inlineStr">
+        <is>
+          <t>Íj</t>
+        </is>
+      </c>
+      <c r="J155" s="7" t="n"/>
+      <c r="K155" s="8" t="inlineStr">
+        <is>
+          <t>A Buzogány növény is (buzogányos káka). A 4. csoporttal közös a honfoglalás-kori hangulat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="n">
+        <v>46326</v>
+      </c>
+      <c r="C156" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>Magyar világörökségi helyszínek</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="n"/>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>Hollókő</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>Aggtelek</t>
+        </is>
+      </c>
+      <c r="H156" s="7" t="inlineStr">
+        <is>
+          <t>Tokaj</t>
+        </is>
+      </c>
+      <c r="I156" s="7" t="inlineStr">
+        <is>
+          <t>Hortobágy</t>
+        </is>
+      </c>
+      <c r="J156" s="7" t="n"/>
+      <c r="K156" s="8" t="inlineStr">
+        <is>
+          <t>Tudásigényes. Tokaj borvidék is, Hortobágy tájegység is - éppen ezért világörökség mindkettő.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B157" s="14" t="n">
+        <v>46326</v>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>Honfoglaló törzsek</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="n"/>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>Nyék</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>Megyer</t>
+        </is>
+      </c>
+      <c r="H157" s="7" t="inlineStr">
+        <is>
+          <t>Tarján</t>
+        </is>
+      </c>
+      <c r="I157" s="7" t="inlineStr">
+        <is>
+          <t>Jenő</t>
+        </is>
+      </c>
+      <c r="J157" s="7" t="n"/>
+      <c r="K157" s="8" t="inlineStr">
+        <is>
+          <t>FŐ CSAPDA: a Jenő keresztnév, a Tarján és a Megyer pedig településnév - ezért a 3. csoport felé húznak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B158" s="14" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>Pénzügyi okmányok</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="n"/>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>Csekk</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>Váltó</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="inlineStr">
+        <is>
+          <t>Kötvény</t>
+        </is>
+      </c>
+      <c r="I158" s="7" t="inlineStr">
+        <is>
+          <t>Nyugta</t>
+        </is>
+      </c>
+      <c r="J158" s="7" t="n"/>
+      <c r="K158" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport. A Váltó vasúti váltó és váltófutás is, a Nyugta a nyugalomra hajaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B159" s="14" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C159" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" s="8" t="inlineStr">
+        <is>
+          <t>Közterhek</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>szja = személyi jövedelemadó</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>Áfa</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>Szja</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="inlineStr">
+        <is>
+          <t>Illeték</t>
+        </is>
+      </c>
+      <c r="I159" s="7" t="inlineStr">
+        <is>
+          <t>Vám</t>
+        </is>
+      </c>
+      <c r="J159" s="7" t="n"/>
+      <c r="K159" s="8" t="inlineStr">
+        <is>
+          <t>Mind a négy valódi magyar közteher. Az 1. csoporttal közös a pénzügyi közeg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B160" s="14" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C160" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>Mértani testek</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="n"/>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>Kúp</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>Gömb</t>
+        </is>
+      </c>
+      <c r="H160" s="7" t="inlineStr">
+        <is>
+          <t>Henger</t>
+        </is>
+      </c>
+      <c r="I160" s="7" t="inlineStr">
+        <is>
+          <t>Hasáb</t>
+        </is>
+      </c>
+      <c r="J160" s="7" t="n"/>
+      <c r="K160" s="8" t="inlineStr">
+        <is>
+          <t>A Henger motorrész is, a Hasáb fahasáb is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B161" s="14" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C161" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>Statisztikai fogalmak</t>
+        </is>
+      </c>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t>A terjedelem a legnagyobb és a legkisebb érték különbsége</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>Terjedelem</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>Szórás</t>
+        </is>
+      </c>
+      <c r="H161" s="7" t="inlineStr">
+        <is>
+          <t>Módusz</t>
+        </is>
+      </c>
+      <c r="I161" s="7" t="inlineStr">
+        <is>
+          <t>Medián</t>
+        </is>
+      </c>
+      <c r="J161" s="7" t="n"/>
+      <c r="K161" s="8" t="inlineStr">
+        <is>
+          <t>FIGYELEM: a Terjedelem 10 karakter, kétsoros doboz kell hozzá. CSAPDA: a 3. csoporttal együtt matekórát idéz, a Terjedelem geometriai fogalomnak hat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B162" s="14" t="n">
+        <v>46328</v>
+      </c>
+      <c r="C162" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>Építészeti elemek</t>
+        </is>
+      </c>
+      <c r="E162" s="8" t="n"/>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>Oromzat</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>Pillér</t>
+        </is>
+      </c>
+      <c r="H162" s="7" t="inlineStr">
+        <is>
+          <t>Boltív</t>
+        </is>
+      </c>
+      <c r="I162" s="7" t="inlineStr">
+        <is>
+          <t>Zsalu</t>
+        </is>
+      </c>
+      <c r="J162" s="7" t="n"/>
+      <c r="K162" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport, de nem triviális. A Pillér átvitt értelemben támaszt is jelent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B163" s="14" t="n">
+        <v>46328</v>
+      </c>
+      <c r="C163" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>Szófajok</t>
+        </is>
+      </c>
+      <c r="E163" s="8" t="n"/>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>Főnév</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>Ige</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="inlineStr">
+        <is>
+          <t>Névmás</t>
+        </is>
+      </c>
+      <c r="I163" s="7" t="inlineStr">
+        <is>
+          <t>Kötőszó</t>
+        </is>
+      </c>
+      <c r="J163" s="7" t="n"/>
+      <c r="K163" s="8" t="inlineStr">
+        <is>
+          <t>Tiszta nyelvtan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B164" s="14" t="n">
+        <v>46328</v>
+      </c>
+      <c r="C164" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D164" s="8" t="inlineStr">
+        <is>
+          <t>Színházi fogalmak</t>
+        </is>
+      </c>
+      <c r="E164" s="8" t="n"/>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>Súgó</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>Díszlet</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="inlineStr">
+        <is>
+          <t>Kulissza</t>
+        </is>
+      </c>
+      <c r="I164" s="7" t="inlineStr">
+        <is>
+          <t>Felvonás</t>
+        </is>
+      </c>
+      <c r="J164" s="7" t="n"/>
+      <c r="K164" s="8" t="inlineStr">
+        <is>
+          <t>A Súgó a programok segítségére is utal, a Felvonás a felvonóra hajaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B165" s="14" t="n">
+        <v>46328</v>
+      </c>
+      <c r="C165" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>Irodalmi műfajok</t>
+        </is>
+      </c>
+      <c r="E165" s="8" t="n"/>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>Elégia</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>Eposz</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>Szonett</t>
+        </is>
+      </c>
+      <c r="I165" s="7" t="inlineStr">
+        <is>
+          <t>Ballada</t>
+        </is>
+      </c>
+      <c r="J165" s="7" t="n"/>
+      <c r="K165" s="8" t="inlineStr">
+        <is>
+          <t>Tudásigényes, és nincs benne tulajdonnév. A 3. csoporttal közös a művészeti közeg: a Ballada színpadi műnek is hathat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B166" s="14" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C166" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t>Hegymászó felszerelés</t>
+        </is>
+      </c>
+      <c r="E166" s="8" t="n"/>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>Kötél</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>Karabiner</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>Hágóvas</t>
+        </is>
+      </c>
+      <c r="I166" s="7" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="J166" s="7" t="n"/>
+      <c r="K166" s="8" t="inlineStr">
+        <is>
+          <t>Belépő csoport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B167" s="14" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C167" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D167" s="8" t="inlineStr">
+        <is>
+          <t>Barlangi képződmények</t>
+        </is>
+      </c>
+      <c r="E167" s="8" t="inlineStr">
+        <is>
+          <t>A szifon vízzel telt barlangszakasz</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>Cseppkő</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>Szifon</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>Kürtő</t>
+        </is>
+      </c>
+      <c r="I167" s="7" t="inlineStr">
+        <is>
+          <t>Terem</t>
+        </is>
+      </c>
+      <c r="J167" s="7" t="n"/>
+      <c r="K167" s="8" t="inlineStr">
+        <is>
+          <t>A Terem ige is (terem a gomba), a Szifon szódásüveg is, a Kürtő kémény is. Az 1. csoporttal közös a barlangászat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B168" s="14" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C168" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D168" s="8" t="inlineStr">
+        <is>
+          <t>Örökléstani fogalmak</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="n"/>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>Gén</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>Mutáció</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>Genom</t>
+        </is>
+      </c>
+      <c r="I168" s="7" t="inlineStr">
+        <is>
+          <t>Klón</t>
+        </is>
+      </c>
+      <c r="J168" s="7" t="n"/>
+      <c r="K168" s="8" t="inlineStr">
+        <is>
+          <t>Tiszta genetika.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B169" s="14" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C169" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>Magyar irodalmi folyóiratok</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="n"/>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>Nyugat</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>Kortárs</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
+          <t>Holmi</t>
+        </is>
+      </c>
+      <c r="I169" s="7" t="inlineStr">
+        <is>
+          <t>Jelenkor</t>
+        </is>
+      </c>
+      <c r="J169" s="7" t="n"/>
+      <c r="K169" s="8" t="inlineStr">
+        <is>
+          <t>FŐ CSAPDA: mind a négy hétköznapi szó is - égtáj, melléknév, cucc, korszak. Tudni kell, hogy léteznek ilyen nevű lapok.</t>
         </is>
       </c>
     </row>
@@ -6447,7 +8351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E385"/>
+  <dimension ref="A1:E673"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -6967,6 +8871,11 @@
           <t>Öv</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6982,6 +8891,11 @@
           <t>Cipő</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6997,6 +8911,11 @@
           <t>Harang</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7012,6 +8931,11 @@
           <t>Pumi</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7027,6 +8951,11 @@
           <t>Fehér</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7042,6 +8971,11 @@
           <t>Volna</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7057,6 +8991,11 @@
           <t>Kuvasz</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7072,6 +9011,11 @@
           <t>Puli</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7087,6 +9031,11 @@
           <t>Poén</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7102,6 +9051,11 @@
           <t>Barack</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7117,6 +9071,11 @@
           <t>Piros</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7132,6 +9091,11 @@
           <t>Makk</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7147,6 +9111,11 @@
           <t>Zöld</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7162,6 +9131,11 @@
           <t>Rigó</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7177,6 +9151,11 @@
           <t>Törköly</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7192,6 +9171,11 @@
           <t>Zserbó</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7207,6 +9191,11 @@
           <t>Ágyú</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7222,6 +9211,11 @@
           <t>Esterházy</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12350,6 +14344,4326 @@
       <c r="C385" t="inlineStr">
         <is>
           <t>Tarantula</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>1</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Golyóstoll</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>2</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Szám</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>3</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Energia</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>4</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Volt</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>5</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Mód</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>6</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Év</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>7</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Munka</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>8</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Erő</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>9</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Eset</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>10</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Láb</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>11</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Dinamó</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>12</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Gyufa</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>13</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Személy</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>14</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Nyomás</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>15</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Szódavíz</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>rsz-025</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>16</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Karát</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>1</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Tört</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>2</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Szünet</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>3</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Hörgő</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>4</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Kereszt</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>5</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Morzsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>6</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Szoba</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>7</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Kő</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>8</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Ütem</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>9</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Írisz</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>10</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Szög</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>11</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Kulcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>12</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Sor</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>13</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Ér</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>14</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Lép</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>15</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Galamb</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>rsz-026</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>16</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Gyök</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>1</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Nyereg</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>2</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Szár</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>3</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Öböl</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>4</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Rügy</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>5</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Far</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>6</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Fok</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>7</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Árboc</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>8</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Medence</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>9</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Kormány</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>10</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Bimbó</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>11</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Bibe</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>12</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Hélium</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>13</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Orr</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>14</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Szén</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>15</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Arany</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>rsz-027</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>16</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Vas</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>1</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Inga</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>2</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Szárny</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>3</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Fény</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>4</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Somlói</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>5</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Árnyék</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>6</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Csőr</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>7</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Toll</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>8</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Begy</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>9</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Rétes</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>10</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Fagylalt</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>11</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Rugó</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>12</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Tükör</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>13</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Lencse</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>14</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Mutató</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>15</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Krémes</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>rsz-028</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>16</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Korona</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>1</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Hozam</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>2</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Soproni</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>3</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Kamat</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>4</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Margó</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>5</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Kínálat</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>6</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Fül</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>7</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Ítélet</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>8</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Kötés</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>9</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Tanú</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>10</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Dreher</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>11</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Vád</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>12</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Borsodi</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>13</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>14</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Kőbányai</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>15</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Gerinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>rsz-029</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>16</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Mérleg</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>1</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Korona</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>2</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Ideg</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>3</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Fakanál</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>4</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Csúcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>5</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Egér</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>6</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Fonák</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>7</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Szél</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>8</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Habverő</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>9</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Gyökér</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>10</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Kukac</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>11</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Zománc</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>12</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Ablak</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>13</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Tepsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>14</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Mappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>15</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Nyél</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>rsz-030</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>16</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Merőkanál</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>1</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Dáridó</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>2</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Vörhenyes</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>3</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Kasza</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>4</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Legényes</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>5</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Ugrós</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>6</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Bál</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>7</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Verbunk</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>8</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Kapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>9</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Molnár</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>10</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Muri</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>11</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Villa</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>12</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Karikázó</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>13</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Mulatság</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>14</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Füsti</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>15</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Gereblye</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>rsz-031</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>16</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Sarlós</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>1</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Gallon</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>2</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Sarok</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>3</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>4</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Hüvelyk</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>5</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Gyűrűs</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>6</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Vese</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>7</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Liter</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>8</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Fog</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>9</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Mérföld</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>10</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Koksz</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>11</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Pint</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>12</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Brikett</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>13</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Mutató</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>14</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Középső</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>15</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>rsz-032</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>16</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Hordó</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>1</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Tizedes</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>2</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Vágat</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>3</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Tám</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>4</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Zászlós</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>5</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Triász</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>6</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Kréta</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>7</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Fagy</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>8</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Perm</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>9</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Súly</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>10</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Tárna</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>11</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Jura</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>12</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Csille</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>13</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Fejtés</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>14</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Hadnagy</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>15</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Őrmester</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>rsz-033</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>16</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Vég</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>1</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Tönk</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>2</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Kalap</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>3</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Oktáv</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>4</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Spóra</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>5</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Nem</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>6</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Kvint</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>7</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Terc</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>8</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Osztály</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>9</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Tölgy</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>10</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Lemez</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>11</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Juhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>12</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Faj</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>13</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Rend</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>14</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Bükk</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>15</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Nyír</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>rsz-034</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>16</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Szekund</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>1</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Flanel</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>2</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Bolyai</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>3</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Dér</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>4</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Neumann</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>5</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Riesz</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>6</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Oláh</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>7</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Köd</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>8</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Zivatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>9</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Jégeső</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>10</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Erdős</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>11</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Kertész</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>12</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Wigner</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>13</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Selyem</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>14</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Gábor</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>15</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Vászon</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>rsz-035</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>16</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Bársony</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>1</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Nyúltvelő</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>2</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Kisagy</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>3</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Pellagra</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>4</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Tabletta</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>5</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Dukát</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>6</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Skorbut</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>7</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Garas</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>8</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Angolkór</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>9</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Peták</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>10</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Kúp</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>11</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Recept</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>12</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Híd</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>13</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Beriberi</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>14</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Talamusz</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>15</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Kenőcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>rsz-036</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>16</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Fillér</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>1</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Zongora</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>2</v>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Rovar</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>3</v>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Asztúr</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>4</v>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Mérnök</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>5</v>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Árpád</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>6</v>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Jagelló</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>7</v>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Habsburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>8</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Galego</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>9</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Évszak</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>10</v>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Anjou</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>11</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Pont</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>12</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Baszk</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>13</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Zárójel</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>14</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Katalán</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>15</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Vessző</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>rsz-037</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>16</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Aposztróf</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>1</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Jancsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>2</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Légnemű</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>3</v>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Szilárd</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>4</v>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Juhfark</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>5</v>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Balaton</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>6</v>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Fertő</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>7</v>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Hévíz</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>8</v>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Kadarka</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>9</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Tarr</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>10</v>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Szabó</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>11</v>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Enyedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>12</v>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Velencei</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>13</v>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Plazma</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>14</v>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Folyékony</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>15</v>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Furmint</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>rsz-038</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>16</v>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Ezerjó</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>1</v>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Tokaj</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>2</v>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Alabárd</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>3</v>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Nyék</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>4</v>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Aggtelek</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>5</v>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Buzogány</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>6</v>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Tarján</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>7</v>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Tündér</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>8</v>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Szablya</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>9</v>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Manó</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>10</v>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Táltos</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>11</v>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Jenő</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>12</v>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Óriás</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>13</v>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Hortobágy</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>14</v>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Megyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>15</v>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Íj</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>rsz-039</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>16</v>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Hollókő</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>1</v>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Váltó</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>2</v>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Csekk</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>3</v>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Vám</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>4</v>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Gömb</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>5</v>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Módusz</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>6</v>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Illeték</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>7</v>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Terjedelem</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>8</v>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Nyugta</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>9</v>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Henger</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>10</v>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Medián</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>11</v>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Szja</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>12</v>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Kúp</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>13</v>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Áfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>14</v>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Szórás</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>15</v>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Hasáb</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>rsz-040</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>16</v>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Kötvény</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>1</v>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Díszlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>2</v>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Szonett</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>3</v>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Pillér</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>4</v>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Főnév</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>5</v>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Oromzat</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>6</v>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Ige</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>7</v>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Boltív</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>8</v>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Kötőszó</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>9</v>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Súgó</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>10</v>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Kulissza</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>11</v>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Eposz</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>12</v>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Felvonás</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>13</v>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Ballada</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>14</v>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Zsalu</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>15</v>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Elégia</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>rsz-041</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>16</v>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Névmás</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>1</v>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Hágóvas</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>2</v>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Cseppkő</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>3</v>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Jelenkor</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>4</v>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Holmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>5</v>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Kürtő</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>6</v>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Kötél</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>7</v>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Genom</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>8</v>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Karabiner</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>9</v>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Nyugat</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>10</v>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Kortárs</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>11</v>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Terem</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>12</v>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Szifon</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>13</v>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Mutáció</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>14</v>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Klón</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>15</v>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>rsz-042</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>16</v>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Gén</t>
         </is>
       </c>
     </row>
@@ -12389,7 +18703,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>rsz-025</t>
+          <t>rsz-033</t>
         </is>
       </c>
       <c r="C2">
@@ -12409,73 +18723,73 @@
     </row>
     <row r="6" ht="27.75" customHeight="1">
       <c r="A6" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+1-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+1-1)</f>
         <v/>
       </c>
       <c r="B6" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+2-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+2-1)</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+3-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+3-1)</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+4-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+4-1)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="27.75" customHeight="1">
       <c r="A7" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+1-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+5-1)</f>
         <v/>
       </c>
       <c r="B7" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+6-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+6-1)</f>
         <v/>
       </c>
       <c r="C7" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+7-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+7-1)</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+8-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+8-1)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="27.75" customHeight="1">
       <c r="A8" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+9-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+9-1)</f>
         <v/>
       </c>
       <c r="B8" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+10-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+10-1)</f>
         <v/>
       </c>
       <c r="C8" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+11-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+11-1)</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+12-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+12-1)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="27.75" customHeight="1">
       <c r="A9" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+13-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+13-1)</f>
         <v/>
       </c>
       <c r="B9" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+14-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+14-1)</f>
         <v/>
       </c>
       <c r="C9" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+15-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+15-1)</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>INDEX(Segéd!$C$2:$C$385,MATCH($B$2,Segéd!$A$2:$A$385,0)+16-1)</f>
+        <f>INDEX(Segéd!$C$2:$C$673,MATCH($B$2,Segéd!$A$2:$A$673,0)+16-1)</f>
         <v/>
       </c>
     </row>
@@ -12516,27 +18830,27 @@
         <v>1</v>
       </c>
       <c r="B23" s="6">
-        <f>INDEX(Feladványok!$D$2:$D$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+1-1)</f>
+        <f>INDEX(Feladványok!$D$2:$D$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+1-1)</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>INDEX(Feladványok!$F$2:$F$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+1-1)</f>
+        <f>INDEX(Feladványok!$F$2:$F$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+1-1)</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>INDEX(Feladványok!$G$2:$G$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+1-1)</f>
+        <f>INDEX(Feladványok!$G$2:$G$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+1-1)</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>INDEX(Feladványok!$H$2:$H$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+1-1)</f>
+        <f>INDEX(Feladványok!$H$2:$H$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+1-1)</f>
         <v/>
       </c>
       <c r="F23" s="6">
-        <f>INDEX(Feladványok!$I$2:$I$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+1-1)</f>
+        <f>INDEX(Feladványok!$I$2:$I$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+1-1)</f>
         <v/>
       </c>
       <c r="G23" s="6">
-        <f>IF(INDEX(Feladványok!$E$2:$E$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+1-1)="","",INDEX(Feladványok!$E$2:$E$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+1-1))</f>
+        <f>IF(INDEX(Feladványok!$E$2:$E$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+1-1)="","",INDEX(Feladványok!$E$2:$E$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+1-1))</f>
         <v/>
       </c>
     </row>
@@ -12545,27 +18859,27 @@
         <v>2</v>
       </c>
       <c r="B24" s="6">
-        <f>INDEX(Feladványok!$D$2:$D$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+2-1)</f>
+        <f>INDEX(Feladványok!$D$2:$D$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+2-1)</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>INDEX(Feladványok!$F$2:$F$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+2-1)</f>
+        <f>INDEX(Feladványok!$F$2:$F$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+2-1)</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>INDEX(Feladványok!$G$2:$G$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+2-1)</f>
+        <f>INDEX(Feladványok!$G$2:$G$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+2-1)</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>INDEX(Feladványok!$H$2:$H$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+2-1)</f>
+        <f>INDEX(Feladványok!$H$2:$H$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+2-1)</f>
         <v/>
       </c>
       <c r="F24" s="6">
-        <f>INDEX(Feladványok!$I$2:$I$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+2-1)</f>
+        <f>INDEX(Feladványok!$I$2:$I$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+2-1)</f>
         <v/>
       </c>
       <c r="G24" s="6">
-        <f>IF(INDEX(Feladványok!$E$2:$E$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+2-1)="","",INDEX(Feladványok!$E$2:$E$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+2-1))</f>
+        <f>IF(INDEX(Feladványok!$E$2:$E$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+2-1)="","",INDEX(Feladványok!$E$2:$E$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+2-1))</f>
         <v/>
       </c>
     </row>
@@ -12574,27 +18888,27 @@
         <v>3</v>
       </c>
       <c r="B25" s="6">
-        <f>INDEX(Feladványok!$D$2:$D$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+3-1)</f>
+        <f>INDEX(Feladványok!$D$2:$D$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+3-1)</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>INDEX(Feladványok!$F$2:$F$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+3-1)</f>
+        <f>INDEX(Feladványok!$F$2:$F$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+3-1)</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>INDEX(Feladványok!$G$2:$G$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+3-1)</f>
+        <f>INDEX(Feladványok!$G$2:$G$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+3-1)</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>INDEX(Feladványok!$H$2:$H$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+3-1)</f>
+        <f>INDEX(Feladványok!$H$2:$H$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+3-1)</f>
         <v/>
       </c>
       <c r="F25" s="6">
-        <f>INDEX(Feladványok!$I$2:$I$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+3-1)</f>
+        <f>INDEX(Feladványok!$I$2:$I$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+3-1)</f>
         <v/>
       </c>
       <c r="G25" s="6">
-        <f>IF(INDEX(Feladványok!$E$2:$E$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+3-1)="","",INDEX(Feladványok!$E$2:$E$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+3-1))</f>
+        <f>IF(INDEX(Feladványok!$E$2:$E$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+3-1)="","",INDEX(Feladványok!$E$2:$E$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+3-1))</f>
         <v/>
       </c>
     </row>
@@ -12603,31 +18917,36 @@
         <v>4</v>
       </c>
       <c r="B26" s="6">
-        <f>INDEX(Feladványok!$D$2:$D$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+4-1)</f>
+        <f>INDEX(Feladványok!$D$2:$D$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+4-1)</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>INDEX(Feladványok!$F$2:$F$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+4-1)</f>
+        <f>INDEX(Feladványok!$F$2:$F$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+4-1)</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>INDEX(Feladványok!$G$2:$G$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+4-1)</f>
+        <f>INDEX(Feladványok!$G$2:$G$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+4-1)</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>INDEX(Feladványok!$H$2:$H$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+4-1)</f>
+        <f>INDEX(Feladványok!$H$2:$H$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+4-1)</f>
         <v/>
       </c>
       <c r="F26" s="6">
-        <f>INDEX(Feladványok!$I$2:$I$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+4-1)</f>
+        <f>INDEX(Feladványok!$I$2:$I$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+4-1)</f>
         <v/>
       </c>
       <c r="G26" s="6">
-        <f>IF(INDEX(Feladványok!$E$2:$E$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+4-1)="","",INDEX(Feladványok!$E$2:$E$97,MATCH($B$2,Feladványok!$A$2:$A$97,0)+4-1))</f>
+        <f>IF(INDEX(Feladványok!$E$2:$E$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+4-1)="","",INDEX(Feladványok!$E$2:$E$169,MATCH($B$2,Feladványok!$A$2:$A$169,0)+4-1))</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Nincs ilyen feladvány" error="Válassz a legördülő listából." promptTitle="Feladvány" prompt="Kattints a nyílra, és válassz feladványt." type="list">
+      <formula1>=feladvany_lista</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
